--- a/docs/build/lakeshore-enterprise-context/source/04_finance_performance/kpi_catalog.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/04_finance_performance/kpi_catalog.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>50.2</t>
         </is>
       </c>
     </row>
@@ -528,22 +528,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Elena Vasquez</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>2.3</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>92.9</t>
         </is>
       </c>
     </row>
@@ -602,12 +602,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>26.3</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>72.6</t>
         </is>
       </c>
     </row>
@@ -656,22 +656,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>86.1</t>
         </is>
       </c>
     </row>
@@ -688,22 +688,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Liam O'Sullivan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>20.8</t>
         </is>
       </c>
     </row>
@@ -720,22 +720,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Ops</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Tomas Halvorsen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>1.6</t>
         </is>
       </c>
     </row>
@@ -752,22 +752,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Priya Natarajan</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>22.1</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ops</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>47.6</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Priya Natarajan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>53.2</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Sofia Marchetti</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>65.6</t>
         </is>
       </c>
     </row>
